--- a/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
@@ -17,6 +17,19 @@
       <family val="2"/>
     </font>
     <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="27.5"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -37,19 +50,6 @@
     </font>
     <font>
       <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -133,18 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -251,7 +251,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>260819</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>88708</xdr:rowOff>
+      <xdr:rowOff>88716</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="789908" cy="44712"/>
     <xdr:pic>
@@ -293,8 +293,8 @@
     <col min="2" max="2" width="0.57" customWidth="1"/>
     <col min="3" max="3" width="1.52" customWidth="1"/>
     <col min="4" max="4" width="22.09" customWidth="1"/>
-    <col min="5" max="5" width="16.08" customWidth="1"/>
-    <col min="6" max="6" width="20.05" customWidth="1"/>
+    <col min="5" max="5" width="16.11" customWidth="1"/>
+    <col min="6" max="6" width="20.02" customWidth="1"/>
     <col min="7" max="7" width="7.00" customWidth="1"/>
     <col min="8" max="8" width="11.52" customWidth="1"/>
     <col min="9" max="9" width="2.02" customWidth="1"/>
@@ -302,14 +302,14 @@
   <sheetData>
     <row r="1" ht="38.37" customHeight="1"/>
     <row r="2" ht="33.00" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">MYRIAD</t>
         </is>
       </c>
     </row>
     <row r="3" ht="9.66" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">HEART OF BURQUITLAM</t>
         </is>
@@ -317,7 +317,7 @@
     </row>
     <row r="4" ht="67.03" customHeight="1"/>
     <row r="5" ht="17.40" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Myriad - Prices at a Glance</t>
         </is>
@@ -325,7 +325,7 @@
     </row>
     <row r="6" ht="8.31" customHeight="1"/>
     <row r="7" ht="12.00" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">October 2021</t>
         </is>
@@ -333,200 +333,200 @@
     </row>
     <row r="8" ht="34.28" customHeight="1"/>
     <row r="9" ht="25.25" customHeight="1">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Suite Type</t>
         </is>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Plan</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Square Feet</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Starting From</t>
         </is>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="1"/>
     </row>
     <row r="10" ht="24.86" customHeight="1">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One Bedroom</t>
         </is>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AT*</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">476-479</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">476 - 479</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$449,900</t>
         </is>
       </c>
-      <c r="H10" s="6"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" ht="21.85" customHeight="1">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">B1 - B7</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">518 - 689</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$499,900</t>
         </is>
       </c>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" ht="21.93" customHeight="1">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" ht="21.97" customHeight="1">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One Bedroom + Den</t>
         </is>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C1 - C6</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">644-769</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">644 - 769</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$599,900</t>
         </is>
       </c>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" ht="23.04" customHeight="1">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" ht="23.16" customHeight="1">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Two Bedroom</t>
         </is>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">D1 - D7</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">801-989</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801 - 989</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$729,900</t>
         </is>
       </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" ht="24.76" customHeight="1">
-      <c r="B14" s="6" t="inlineStr">
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" ht="24.50" customHeight="1">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Two Bedroom + Den</t>
         </is>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">E1 - E7</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">834 - 1,062</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$749,900</t>
         </is>
       </c>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" ht="24.43" customHeight="1">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" ht="24.53" customHeight="1">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Three Bedroom</t>
         </is>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F11</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,023</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$929,900</t>
         </is>
       </c>
-      <c r="H15" s="6"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" ht="21.03" customHeight="1">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Townhomes</t>
         </is>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TH1- TH4</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TH1 - TH4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,338 - 1,553</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$1,249,900</t>
         </is>
       </c>
-      <c r="H16" s="6"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" ht="36.02" customHeight="1"/>
     <row r="18" ht="12.00" customHeight="1">
@@ -568,17 +568,16 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="2.00" customHeight="1"/>
-    <row r="28" ht="12.00" customHeight="1">
-      <c r="D28" s="7" t="inlineStr">
+    <row r="27" ht="12.11" customHeight="1">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 730 days.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="2.08" customHeight="1"/>
-    <row r="30" ht="12.60" customHeight="1">
-      <c r="D30" s="8" t="inlineStr">
+    <row r="28" ht="2.66" customHeight="1"/>
+    <row r="29" ht="12.60" customHeight="1">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -611,44 +610,43 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="56.61" customHeight="1"/>
-    <row r="32" ht="7.67" customHeight="1">
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prices do not include GST, may change without notice and are subject to availability. Sulte sizes may vary on final Strata Plan. Concert reserves the right to</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="6.89" customHeight="1">
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">make modifications and changes to floorplans, project design, specifications and features. October 2021. CONCERT REALTY SERVICES LTD. E. &amp;O.E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="54.63" customHeight="1"/>
-    <row r="35" ht="9.79" customHeight="1">
-      <c r="B35" s="12" t="inlineStr">
+    <row r="30" ht="57.19" customHeight="1"/>
+    <row r="31" ht="7.67" customHeight="1">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rices do not include GST, may change without notice and are subject to availability. Sulte sizes may vary on final Strata Plan. Concert reserves the right t</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="6.31" customHeight="1">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">make modifications and changes to floorplans, project design, specifications and features. October 2021. CONCERT REALTY SERVICES LTD. E.&amp;O.E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54.34" customHeight="1"/>
+    <row r="34" ht="10.36" customHeight="1">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">MyriadbyConcert.com</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="9.79" customHeight="1">
-      <c r="B36" s="13" t="inlineStr">
+    <row r="35" ht="10.36" customHeight="1">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">101 - 511 Clarke Road, Coquitlam, BC V3J 0J1</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="2.00" customHeight="1"/>
-    <row r="38" ht="9.60" customHeight="1">
-      <c r="B38" s="14" t="inlineStr">
+    <row r="36" ht="9.98" customHeight="1">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">604.335.0696 | Admin.Myriad@ConcertProperties.com</t>
         </is>
       </c>
-      <c r="H38" s="15" t="inlineStr">
+      <c r="H36" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">CONCERT®</t>
         </is>
@@ -656,10 +654,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A7:I7"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="B10:D10"/>
@@ -676,19 +670,23 @@
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="D20:I20"/>
     <mergeCell ref="D22:I22"/>
     <mergeCell ref="D24:I24"/>
     <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B34:I34"/>
     <mergeCell ref="B35:I35"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="H36:I36"/>
   </mergeCells>
   <pageMargins left="0.46" right="1.03" top="0.29" bottom="0.3" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>

--- a/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -30,6 +30,13 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="27.5"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -49,6 +56,13 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -98,6 +112,7 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -124,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -139,16 +154,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -169,6 +181,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -302,14 +320,14 @@
   <sheetData>
     <row r="1" ht="38.37" customHeight="1"/>
     <row r="2" ht="33.00" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MYRIAD</t>
         </is>
       </c>
     </row>
     <row r="3" ht="9.66" customHeight="1">
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">HEART OF BURQUITLAM</t>
         </is>
@@ -317,7 +335,7 @@
     </row>
     <row r="4" ht="67.03" customHeight="1"/>
     <row r="5" ht="17.40" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Myriad - Prices at a Glance</t>
         </is>
@@ -325,7 +343,7 @@
     </row>
     <row r="6" ht="8.31" customHeight="1"/>
     <row r="7" ht="12.00" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">October 2021</t>
         </is>
@@ -365,14 +383,14 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AT*</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">476 - 479</t>
+          <t xml:space="preserve">476-479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -393,7 +411,25 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">518 - 689</t>
+          <r>
+            <rPr>
+              <sz val="12.0"/>
+              <color rgb="FF000000"/>
+              <rFont val="Arial"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">518 -</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12.0"/>
+              <color rgb="FF000000"/>
+              <rFont val="Arial"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve"> 689</t>
+          </r>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -418,7 +454,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">644 - 769</t>
+          <t xml:space="preserve">644-769</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -443,7 +479,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801 - 989</t>
+          <t xml:space="preserve">801-989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -468,7 +504,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834 - 1,062</t>
+          <t xml:space="preserve">834-1,062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -518,7 +554,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,338 - 1,553</t>
+          <t xml:space="preserve">1,338-1,553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -530,7 +566,7 @@
     </row>
     <row r="17" ht="36.02" customHeight="1"/>
     <row r="18" ht="12.00" customHeight="1">
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Deposit Structure:</t>
         </is>
@@ -538,7 +574,7 @@
     </row>
     <row r="19" ht="10.12" customHeight="1"/>
     <row r="20" ht="12.60" customHeight="1">
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">•  Initial $10,000 bank draft due upon signing Offer to Purchase and Agreement Sale;</t>
         </is>
@@ -546,7 +582,7 @@
     </row>
     <row r="21" ht="2.00" customHeight="1"/>
     <row r="22" ht="12.00" customHeight="1">
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% within 7 days (less $10,000 initial deposit) upon signing;</t>
         </is>
@@ -554,7 +590,7 @@
     </row>
     <row r="23" ht="2.00" customHeight="1"/>
     <row r="24" ht="11.40" customHeight="1">
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 180 days;</t>
         </is>
@@ -562,14 +598,14 @@
     </row>
     <row r="25" ht="2.00" customHeight="1"/>
     <row r="26" ht="12.00" customHeight="1">
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 365 days;</t>
         </is>
       </c>
     </row>
     <row r="27" ht="12.11" customHeight="1">
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 730 days.</t>
         </is>
@@ -577,7 +613,7 @@
     </row>
     <row r="28" ht="2.66" customHeight="1"/>
     <row r="29" ht="12.60" customHeight="1">
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -612,14 +648,14 @@
     </row>
     <row r="30" ht="57.19" customHeight="1"/>
     <row r="31" ht="7.67" customHeight="1">
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">rices do not include GST, may change without notice and are subject to availability. Sulte sizes may vary on final Strata Plan. Concert reserves the right t</t>
         </is>
       </c>
     </row>
     <row r="32" ht="6.31" customHeight="1">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">make modifications and changes to floorplans, project design, specifications and features. October 2021. CONCERT REALTY SERVICES LTD. E.&amp;O.E.</t>
         </is>
@@ -627,26 +663,26 @@
     </row>
     <row r="33" ht="54.34" customHeight="1"/>
     <row r="34" ht="10.36" customHeight="1">
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">MyriadbyConcert.com</t>
         </is>
       </c>
     </row>
     <row r="35" ht="10.36" customHeight="1">
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">101 - 511 Clarke Road, Coquitlam, BC V3J 0J1</t>
         </is>
       </c>
     </row>
     <row r="36" ht="9.98" customHeight="1">
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">604.335.0696 | Admin.Myriad@ConcertProperties.com</t>
         </is>
       </c>
-      <c r="H36" s="15" t="inlineStr">
+      <c r="H36" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">CONCERT®</t>
         </is>

--- a/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
@@ -37,7 +37,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="27.5"/>
+      <sz val="21.7"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -266,8 +266,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>260819</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>495556</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>88716</xdr:rowOff>
     </xdr:from>
@@ -308,14 +308,11 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.84" customWidth="1"/>
-    <col min="2" max="2" width="0.57" customWidth="1"/>
-    <col min="3" max="3" width="1.52" customWidth="1"/>
-    <col min="4" max="4" width="22.09" customWidth="1"/>
-    <col min="5" max="5" width="16.11" customWidth="1"/>
-    <col min="6" max="6" width="20.02" customWidth="1"/>
-    <col min="7" max="7" width="7.00" customWidth="1"/>
-    <col min="8" max="8" width="11.52" customWidth="1"/>
-    <col min="9" max="9" width="2.02" customWidth="1"/>
+    <col min="2" max="2" width="25.61" customWidth="1"/>
+    <col min="3" max="3" width="16.11" customWidth="1"/>
+    <col min="4" max="4" width="20.02" customWidth="1"/>
+    <col min="5" max="5" width="19.24" customWidth="1"/>
+    <col min="6" max="6" width="2.02" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="38.37" customHeight="1"/>
@@ -327,7 +324,7 @@
       </c>
     </row>
     <row r="3" ht="9.66" customHeight="1">
-      <c r="C3" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">HEART OF BURQUITLAM</t>
         </is>
@@ -356,24 +353,21 @@
           <t xml:space="preserve">Suite Type</t>
         </is>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Square Feet</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Square Feet</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
           <t xml:space="preserve">Starting From</t>
         </is>
       </c>
-      <c r="H9" s="1"/>
     </row>
     <row r="10" ht="24.86" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
@@ -381,35 +375,30 @@
           <t xml:space="preserve">One Bedroom</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AT*</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">476-479</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$449,900</t>
         </is>
       </c>
-      <c r="H10" s="2"/>
     </row>
     <row r="11" ht="21.85" customHeight="1">
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">B1 - B7</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -432,12 +421,11 @@
           </r>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$499,900</t>
         </is>
       </c>
-      <c r="H11" s="2"/>
     </row>
     <row r="12" ht="21.97" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
@@ -445,24 +433,21 @@
           <t xml:space="preserve">One Bedroom + Den</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C1 - C6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">644-769</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1 - C6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">644-769</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$599,900</t>
         </is>
       </c>
-      <c r="H12" s="2"/>
     </row>
     <row r="13" ht="23.16" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
@@ -470,24 +455,21 @@
           <t xml:space="preserve">Two Bedroom</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1 - D7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801-989</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1 - D7</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">801-989</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$729,900</t>
         </is>
       </c>
-      <c r="H13" s="2"/>
     </row>
     <row r="14" ht="24.50" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
@@ -495,24 +477,21 @@
           <t xml:space="preserve">Two Bedroom + Den</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1 - E7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">834-1,062</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1 - E7</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834-1,062</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$749,900</t>
         </is>
       </c>
-      <c r="H14" s="2"/>
     </row>
     <row r="15" ht="24.53" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
@@ -520,24 +499,21 @@
           <t xml:space="preserve">Three Bedroom</t>
         </is>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,023</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1,023</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$929,900</t>
         </is>
       </c>
-      <c r="H15" s="2"/>
     </row>
     <row r="16" ht="21.03" customHeight="1">
       <c r="B16" s="2" t="inlineStr">
@@ -545,24 +521,21 @@
           <t xml:space="preserve">Townhomes</t>
         </is>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TH1 - TH4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,338-1,553</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TH1 - TH4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1,338-1,553</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$1,249,900</t>
         </is>
       </c>
-      <c r="H16" s="2"/>
     </row>
     <row r="17" ht="36.02" customHeight="1"/>
     <row r="18" ht="12.00" customHeight="1">
@@ -574,7 +547,7 @@
     </row>
     <row r="19" ht="10.12" customHeight="1"/>
     <row r="20" ht="12.60" customHeight="1">
-      <c r="D20" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">•  Initial $10,000 bank draft due upon signing Offer to Purchase and Agreement Sale;</t>
         </is>
@@ -582,7 +555,7 @@
     </row>
     <row r="21" ht="2.00" customHeight="1"/>
     <row r="22" ht="12.00" customHeight="1">
-      <c r="D22" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% within 7 days (less $10,000 initial deposit) upon signing;</t>
         </is>
@@ -590,7 +563,7 @@
     </row>
     <row r="23" ht="2.00" customHeight="1"/>
     <row r="24" ht="11.40" customHeight="1">
-      <c r="D24" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 180 days;</t>
         </is>
@@ -598,14 +571,14 @@
     </row>
     <row r="25" ht="2.00" customHeight="1"/>
     <row r="26" ht="12.00" customHeight="1">
-      <c r="D26" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 365 days;</t>
         </is>
       </c>
     </row>
     <row r="27" ht="12.11" customHeight="1">
-      <c r="D27" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 730 days.</t>
         </is>
@@ -613,7 +586,7 @@
     </row>
     <row r="28" ht="2.66" customHeight="1"/>
     <row r="29" ht="12.60" customHeight="1">
-      <c r="D29" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -682,47 +655,31 @@
           <t xml:space="preserve">604.335.0696 | Admin.Myriad@ConcertProperties.com</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">CONCERT®</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="H36:I36"/>
+  <mergeCells count="17">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:F36"/>
   </mergeCells>
   <pageMargins left="0.46" right="1.03" top="0.29" bottom="0.3" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>

--- a/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -43,7 +43,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="7.5"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -95,18 +95,6 @@
     <font>
       <b/>
       <sz val="7.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="7.5"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -139,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -181,12 +169,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -205,7 +187,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="491830" cy="59616"/>
+    <xdr:ext cx="476926" cy="59616"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1"/>
@@ -222,7 +204,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="491830" cy="59616"/>
+          <a:ext cx="476926" cy="59616"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -264,39 +246,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>495556</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>88716</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="789908" cy="44712"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="789908" cy="44712"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -307,10 +256,10 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.84" customWidth="1"/>
-    <col min="2" max="2" width="25.61" customWidth="1"/>
-    <col min="3" max="3" width="16.11" customWidth="1"/>
-    <col min="4" max="4" width="20.02" customWidth="1"/>
+    <col min="1" max="1" width="8.51" customWidth="1"/>
+    <col min="2" max="2" width="25.94" customWidth="1"/>
+    <col min="3" max="3" width="16.08" customWidth="1"/>
+    <col min="4" max="4" width="20.05" customWidth="1"/>
     <col min="5" max="5" width="19.24" customWidth="1"/>
     <col min="6" max="6" width="2.02" customWidth="1"/>
   </cols>
@@ -323,14 +272,14 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="9.66" customHeight="1">
+    <row r="3" ht="8.76" customHeight="1">
       <c r="B3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">HEART OF BURQUITLAM</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="67.03" customHeight="1"/>
+    <row r="4" ht="67.93" customHeight="1"/>
     <row r="5" ht="17.40" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -342,12 +291,30 @@
     <row r="7" ht="12.00" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">October 2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34.28" customHeight="1"/>
-    <row r="9" ht="25.25" customHeight="1">
+          <r>
+            <rPr>
+              <b/>
+              <sz val="10.0"/>
+              <color rgb="FF000000"/>
+              <rFont val="Arial"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">October</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10.0"/>
+              <color rgb="FF000000"/>
+              <rFont val="Arial"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve"> 2021</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34.76" customHeight="1"/>
+    <row r="9" ht="24.77" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Suite Type</t>
@@ -391,7 +358,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="21.85" customHeight="1">
+    <row r="11" ht="21.83" customHeight="1">
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -427,7 +394,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="21.97" customHeight="1">
+    <row r="12" ht="22.02" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One Bedroom + Den</t>
@@ -449,7 +416,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="23.16" customHeight="1">
+    <row r="13" ht="23.15" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Two Bedroom</t>
@@ -471,7 +438,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="24.50" customHeight="1">
+    <row r="14" ht="24.48" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Two Bedroom + Den</t>
@@ -577,16 +544,17 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="12.11" customHeight="1">
-      <c r="B27" s="8" t="inlineStr">
+    <row r="27" ht="2.00" customHeight="1"/>
+    <row r="28" ht="12.00" customHeight="1">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 730 days.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="2.66" customHeight="1"/>
-    <row r="29" ht="12.60" customHeight="1">
-      <c r="B29" s="9" t="inlineStr">
+    <row r="29" ht="2.08" customHeight="1"/>
+    <row r="30" ht="12.60" customHeight="1">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -619,43 +587,44 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="57.19" customHeight="1"/>
-    <row r="31" ht="7.67" customHeight="1">
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rices do not include GST, may change without notice and are subject to availability. Sulte sizes may vary on final Strata Plan. Concert reserves the right t</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="6.31" customHeight="1">
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">make modifications and changes to floorplans, project design, specifications and features. October 2021. CONCERT REALTY SERVICES LTD. E.&amp;O.E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="54.34" customHeight="1"/>
-    <row r="34" ht="10.36" customHeight="1">
-      <c r="B34" s="13" t="inlineStr">
+    <row r="31" ht="57.19" customHeight="1"/>
+    <row r="32" ht="7.67" customHeight="1">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prices do not include GST, may change without notice and are subject to availability. Sulte sizes may vary on final Strata Plan. Concert reserves the right to</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="6.31" customHeight="1">
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nake modifications and changes to floorplans, project design, specifications and features. October 2021. CONCERT REALTY SERVICES LTD. E.8O.!</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54.63" customHeight="1"/>
+    <row r="35" ht="9.79" customHeight="1">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">MyriadbyConcert.com</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="10.36" customHeight="1">
-      <c r="B35" s="14" t="inlineStr">
+    <row r="36" ht="9.79" customHeight="1">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">101 - 511 Clarke Road, Coquitlam, BC V3J 0J1</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="9.98" customHeight="1">
-      <c r="B36" s="15" t="inlineStr">
+    <row r="37" ht="2.00" customHeight="1"/>
+    <row r="38" ht="9.00" customHeight="1">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">604.335.0696 | Admin.Myriad@ConcertProperties.com</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">CONCERT®</t>
         </is>
@@ -672,14 +641,14 @@
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B33:F33"/>
     <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:F38"/>
   </mergeCells>
   <pageMargins left="0.46" right="1.03" top="0.29" bottom="0.3" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>

--- a/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
@@ -37,7 +37,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="21.7"/>
+      <sz val="21.4"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -130,13 +130,13 @@
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -265,21 +265,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="38.37" customHeight="1"/>
-    <row r="2" ht="33.00" customHeight="1">
+    <row r="2" ht="32.54" customHeight="1">
       <c r="B2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MYRIAD</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="8.76" customHeight="1">
+    <row r="3" ht="9.00" customHeight="1">
       <c r="B3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">HEART OF BURQUITLAM</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="67.93" customHeight="1"/>
+    <row r="4" ht="67.00" customHeight="1"/>
     <row r="5" ht="17.40" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -287,7 +287,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="8.31" customHeight="1"/>
+    <row r="6" ht="8.90" customHeight="1"/>
     <row r="7" ht="12.00" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
@@ -313,8 +313,8 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="34.76" customHeight="1"/>
-    <row r="9" ht="24.77" customHeight="1">
+    <row r="8" ht="34.39" customHeight="1"/>
+    <row r="9" ht="25.12" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Suite Type</t>
@@ -336,7 +336,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24.86" customHeight="1">
+    <row r="10" ht="25.58" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One Bedroom</t>
@@ -358,7 +358,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="21.83" customHeight="1">
+    <row r="11" ht="22.19" customHeight="1">
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -394,7 +394,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="22.02" customHeight="1">
+    <row r="12" ht="21.47" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One Bedroom + Den</t>
@@ -416,7 +416,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="23.15" customHeight="1">
+    <row r="13" ht="22.66" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Two Bedroom</t>
@@ -438,7 +438,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="24.48" customHeight="1">
+    <row r="14" ht="25.14" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Two Bedroom + Den</t>
@@ -460,7 +460,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24.53" customHeight="1">
+    <row r="15" ht="24.67" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Three Bedroom</t>
@@ -482,7 +482,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="21.03" customHeight="1">
+    <row r="16" ht="20.36" customHeight="1">
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Townhomes</t>
@@ -504,7 +504,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="36.02" customHeight="1"/>
+    <row r="17" ht="36.45" customHeight="1"/>
     <row r="18" ht="12.00" customHeight="1">
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="10.12" customHeight="1"/>
+    <row r="19" ht="10.42" customHeight="1"/>
     <row r="20" ht="12.60" customHeight="1">
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -520,41 +520,37 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="2.00" customHeight="1"/>
-    <row r="22" ht="12.00" customHeight="1">
+    <row r="21" ht="2.44" customHeight="1"/>
+    <row r="22" ht="10.79" customHeight="1">
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">•  5% within 7 days (less $10,000 initial deposit) upon signing;</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="2.00" customHeight="1"/>
-    <row r="24" ht="11.40" customHeight="1">
-      <c r="B24" s="10" t="inlineStr">
+          <t xml:space="preserve">pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="12.95" customHeight="1">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 180 days;</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="2.00" customHeight="1"/>
-    <row r="26" ht="12.00" customHeight="1">
-      <c r="B26" s="8" t="inlineStr">
+    <row r="24" ht="13.53" customHeight="1">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 365 days;</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="2.00" customHeight="1"/>
-    <row r="28" ht="12.00" customHeight="1">
-      <c r="B28" s="8" t="inlineStr">
+    <row r="25" ht="12.69" customHeight="1">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 730 days.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="2.08" customHeight="1"/>
-    <row r="30" ht="12.60" customHeight="1">
-      <c r="B30" s="9" t="inlineStr">
+    <row r="26" ht="14.68" customHeight="1">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -587,46 +583,45 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="57.19" customHeight="1"/>
-    <row r="32" ht="7.67" customHeight="1">
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prices do not include GST, may change without notice and are subject to availability. Sulte sizes may vary on final Strata Plan. Concert reserves the right to</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="6.31" customHeight="1">
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nake modifications and changes to floorplans, project design, specifications and features. October 2021. CONCERT REALTY SERVICES LTD. E.8O.!</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="54.63" customHeight="1"/>
-    <row r="35" ht="9.79" customHeight="1">
-      <c r="B35" s="13" t="inlineStr">
+    <row r="27" ht="57.18" customHeight="1"/>
+    <row r="28" ht="6.89" customHeight="1">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prices do not include GST, may change without notice and are subject to availability. Suite sizes may vary on final Strata Plan. Concert reserves the right to</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="7.67" customHeight="1">
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">make modifications and changes to floorplans, project design, specifications and features. October 2021. CONCERT REALTY SERVICES LTD. E.&amp;O.E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54.35" customHeight="1"/>
+    <row r="31" ht="9.21" customHeight="1">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">MyriadbyConcert.com</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="9.79" customHeight="1">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101 - 511 Clarke Road, Coquitlam, BC V3J 0J1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="2.00" customHeight="1"/>
-    <row r="38" ht="9.00" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
+    <row r="32" ht="9.21" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101 - 511 Clarke Road, Coquitlam, BC V3J 0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="10.83" customHeight="1">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">604.335.0696 | Admin.Myriad@ConcertProperties.com</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONCERT®</t>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONCERT'</t>
         </is>
       </c>
     </row>
@@ -639,16 +634,16 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B31:F31"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
   </mergeCells>
   <pageMargins left="0.46" right="1.03" top="0.29" bottom="0.3" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>

--- a/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePhoto.xlsx
@@ -220,7 +220,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>193751</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1311546" cy="59616"/>
+    <xdr:ext cx="1311546" cy="298079"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 2"/>
@@ -237,7 +237,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1311546" cy="59616"/>
+          <a:ext cx="1311546" cy="298079"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
